--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122234132</v>
+        <v>122234131</v>
       </c>
       <c r="B2" t="n">
         <v>94947</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582147</v>
+        <v>582159</v>
       </c>
       <c r="R2" t="n">
-        <v>6542531</v>
+        <v>6542499</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122234131</v>
+        <v>122234132</v>
       </c>
       <c r="B4" t="n">
         <v>94947</v>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582159</v>
+        <v>582147</v>
       </c>
       <c r="R4" t="n">
-        <v>6542499</v>
+        <v>6542531</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122234131</v>
       </c>
       <c r="B2" t="n">
-        <v>94947</v>
+        <v>94957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122234135</v>
+        <v>122234132</v>
       </c>
       <c r="B3" t="n">
-        <v>100441</v>
+        <v>94957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582182</v>
+        <v>582147</v>
       </c>
       <c r="R3" t="n">
-        <v>6542731</v>
+        <v>6542531</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122234132</v>
+        <v>122234135</v>
       </c>
       <c r="B4" t="n">
-        <v>94947</v>
+        <v>100451</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582147</v>
+        <v>582182</v>
       </c>
       <c r="R4" t="n">
-        <v>6542531</v>
+        <v>6542731</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
         <v>122234130</v>
       </c>
       <c r="B5" t="n">
-        <v>91397</v>
+        <v>91407</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122234131</v>
+        <v>122234130</v>
       </c>
       <c r="B2" t="n">
-        <v>94957</v>
+        <v>91407</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582159</v>
+        <v>582050</v>
       </c>
       <c r="R2" t="n">
-        <v>6542499</v>
+        <v>6542447</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122234132</v>
+        <v>122234131</v>
       </c>
       <c r="B3" t="n">
         <v>94957</v>
@@ -835,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582147</v>
+        <v>582159</v>
       </c>
       <c r="R3" t="n">
-        <v>6542531</v>
+        <v>6542499</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122234135</v>
+        <v>122234132</v>
       </c>
       <c r="B4" t="n">
-        <v>100451</v>
+        <v>94957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582182</v>
+        <v>582147</v>
       </c>
       <c r="R4" t="n">
-        <v>6542731</v>
+        <v>6542531</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234130</v>
+        <v>122234135</v>
       </c>
       <c r="B5" t="n">
-        <v>91407</v>
+        <v>100451</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,30 +1042,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582050</v>
+        <v>582182</v>
       </c>
       <c r="R5" t="n">
-        <v>6542447</v>
+        <v>6542731</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122234130</v>
       </c>
       <c r="B2" t="n">
-        <v>91407</v>
+        <v>91419</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122234131</v>
+        <v>122234132</v>
       </c>
       <c r="B3" t="n">
-        <v>94957</v>
+        <v>94969</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582159</v>
+        <v>582147</v>
       </c>
       <c r="R3" t="n">
-        <v>6542499</v>
+        <v>6542531</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122234132</v>
+        <v>122234135</v>
       </c>
       <c r="B4" t="n">
-        <v>94957</v>
+        <v>100463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582147</v>
+        <v>582182</v>
       </c>
       <c r="R4" t="n">
-        <v>6542531</v>
+        <v>6542731</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234135</v>
+        <v>122234131</v>
       </c>
       <c r="B5" t="n">
-        <v>100451</v>
+        <v>94969</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582182</v>
+        <v>582159</v>
       </c>
       <c r="R5" t="n">
-        <v>6542731</v>
+        <v>6542499</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122234130</v>
       </c>
       <c r="B2" t="n">
-        <v>91419</v>
+        <v>91424</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122234132</v>
+        <v>122234131</v>
       </c>
       <c r="B3" t="n">
-        <v>94969</v>
+        <v>94974</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582147</v>
+        <v>582159</v>
       </c>
       <c r="R3" t="n">
-        <v>6542531</v>
+        <v>6542499</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +913,7 @@
         <v>122234135</v>
       </c>
       <c r="B4" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234131</v>
+        <v>122234132</v>
       </c>
       <c r="B5" t="n">
-        <v>94969</v>
+        <v>94974</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582159</v>
+        <v>582147</v>
       </c>
       <c r="R5" t="n">
-        <v>6542499</v>
+        <v>6542531</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122234130</v>
+        <v>122234135</v>
       </c>
       <c r="B2" t="n">
-        <v>91424</v>
+        <v>100477</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582050</v>
+        <v>582182</v>
       </c>
       <c r="R2" t="n">
-        <v>6542447</v>
+        <v>6542731</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +789,7 @@
         <v>122234131</v>
       </c>
       <c r="B3" t="n">
-        <v>94974</v>
+        <v>94983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,11 +803,6 @@
       </c>
       <c r="E3" t="n">
         <v>2180</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -910,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122234135</v>
+        <v>122234132</v>
       </c>
       <c r="B4" t="n">
-        <v>100468</v>
+        <v>94983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +913,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>2180</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582182</v>
+        <v>582147</v>
       </c>
       <c r="R4" t="n">
-        <v>6542731</v>
+        <v>6542531</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234132</v>
+        <v>122234130</v>
       </c>
       <c r="B5" t="n">
-        <v>94974</v>
+        <v>91429</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,27 +1024,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
+        <v>6031</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582147</v>
+        <v>582050</v>
       </c>
       <c r="R5" t="n">
-        <v>6542531</v>
+        <v>6542447</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122234132</v>
+        <v>122234130</v>
       </c>
       <c r="B4" t="n">
-        <v>94983</v>
+        <v>91429</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,22 +913,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582147</v>
+        <v>582050</v>
       </c>
       <c r="R4" t="n">
-        <v>6542531</v>
+        <v>6542447</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234130</v>
+        <v>122234132</v>
       </c>
       <c r="B5" t="n">
-        <v>91429</v>
+        <v>94983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,25 +1027,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582050</v>
+        <v>582147</v>
       </c>
       <c r="R5" t="n">
-        <v>6542447</v>
+        <v>6542531</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122234135</v>
+        <v>122234130</v>
       </c>
       <c r="B2" t="n">
-        <v>100477</v>
+        <v>91442</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,22 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>6031</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582182</v>
+        <v>582050</v>
       </c>
       <c r="R2" t="n">
-        <v>6542731</v>
+        <v>6542447</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -749,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122234131</v>
+        <v>122234135</v>
       </c>
       <c r="B3" t="n">
-        <v>94983</v>
+        <v>100490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,16 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582159</v>
+        <v>582182</v>
       </c>
       <c r="R3" t="n">
-        <v>6542499</v>
+        <v>6542731</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -860,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122234130</v>
+        <v>122234131</v>
       </c>
       <c r="B4" t="n">
-        <v>91429</v>
+        <v>94996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,25 +926,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6031</v>
+        <v>2180</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582050</v>
+        <v>582159</v>
       </c>
       <c r="R4" t="n">
-        <v>6542447</v>
+        <v>6542499</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -974,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1029,7 @@
         <v>122234132</v>
       </c>
       <c r="B5" t="n">
-        <v>94983</v>
+        <v>94996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,6 +1043,11 @@
       </c>
       <c r="E5" t="n">
         <v>2180</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122234130</v>
+        <v>122234135</v>
       </c>
       <c r="B2" t="n">
-        <v>91442</v>
+        <v>100503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582050</v>
+        <v>582182</v>
       </c>
       <c r="R2" t="n">
-        <v>6542447</v>
+        <v>6542731</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122234135</v>
+        <v>122234132</v>
       </c>
       <c r="B3" t="n">
-        <v>100490</v>
+        <v>95009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582182</v>
+        <v>582147</v>
       </c>
       <c r="R3" t="n">
-        <v>6542731</v>
+        <v>6542531</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122234131</v>
+        <v>122234130</v>
       </c>
       <c r="B4" t="n">
-        <v>94996</v>
+        <v>91455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,27 +923,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582159</v>
+        <v>582050</v>
       </c>
       <c r="R4" t="n">
-        <v>6542499</v>
+        <v>6542447</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234132</v>
+        <v>122234131</v>
       </c>
       <c r="B5" t="n">
-        <v>94996</v>
+        <v>95009</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582147</v>
+        <v>582159</v>
       </c>
       <c r="R5" t="n">
-        <v>6542531</v>
+        <v>6542499</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122234135</v>
+        <v>122234131</v>
       </c>
       <c r="B2" t="n">
-        <v>100503</v>
+        <v>95009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582182</v>
+        <v>582159</v>
       </c>
       <c r="R2" t="n">
-        <v>6542731</v>
+        <v>6542499</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122234132</v>
+        <v>122234130</v>
       </c>
       <c r="B3" t="n">
-        <v>95009</v>
+        <v>91455</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,27 +807,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582147</v>
+        <v>582050</v>
       </c>
       <c r="R3" t="n">
-        <v>6542531</v>
+        <v>6542447</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122234130</v>
+        <v>122234132</v>
       </c>
       <c r="B4" t="n">
-        <v>91455</v>
+        <v>95009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,30 +926,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582050</v>
+        <v>582147</v>
       </c>
       <c r="R4" t="n">
-        <v>6542447</v>
+        <v>6542531</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234131</v>
+        <v>122234135</v>
       </c>
       <c r="B5" t="n">
-        <v>95009</v>
+        <v>100503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582159</v>
+        <v>582182</v>
       </c>
       <c r="R5" t="n">
-        <v>6542499</v>
+        <v>6542731</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122234131</v>
+        <v>122234130</v>
       </c>
       <c r="B2" t="n">
-        <v>95009</v>
+        <v>91456</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582159</v>
+        <v>582050</v>
       </c>
       <c r="R2" t="n">
-        <v>6542499</v>
+        <v>6542447</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122234130</v>
+        <v>122234132</v>
       </c>
       <c r="B3" t="n">
-        <v>91455</v>
+        <v>95011</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +810,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582050</v>
+        <v>582147</v>
       </c>
       <c r="R3" t="n">
-        <v>6542447</v>
+        <v>6542531</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122234132</v>
+        <v>122234131</v>
       </c>
       <c r="B4" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582147</v>
+        <v>582159</v>
       </c>
       <c r="R4" t="n">
-        <v>6542531</v>
+        <v>6542499</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1029,7 @@
         <v>122234135</v>
       </c>
       <c r="B5" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122234131</v>
+        <v>122234135</v>
       </c>
       <c r="B4" t="n">
-        <v>95011</v>
+        <v>100506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582159</v>
+        <v>582182</v>
       </c>
       <c r="R4" t="n">
-        <v>6542499</v>
+        <v>6542731</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234135</v>
+        <v>122234131</v>
       </c>
       <c r="B5" t="n">
-        <v>100506</v>
+        <v>95011</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582182</v>
+        <v>582159</v>
       </c>
       <c r="R5" t="n">
-        <v>6542731</v>
+        <v>6542499</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122234130</v>
+        <v>122234133</v>
       </c>
       <c r="B2" t="n">
-        <v>91456</v>
+        <v>97188</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582050</v>
+        <v>582206</v>
       </c>
       <c r="R2" t="n">
-        <v>6542447</v>
+        <v>6542637</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122234132</v>
+        <v>122234130</v>
       </c>
       <c r="B3" t="n">
-        <v>95011</v>
+        <v>91456</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,27 +803,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582147</v>
+        <v>582050</v>
       </c>
       <c r="R3" t="n">
-        <v>6542531</v>
+        <v>6542447</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122234135</v>
+        <v>122234132</v>
       </c>
       <c r="B4" t="n">
-        <v>100506</v>
+        <v>95011</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,13 +950,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582182</v>
+        <v>582147</v>
       </c>
       <c r="R4" t="n">
-        <v>6542731</v>
+        <v>6542531</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234131</v>
+        <v>122234135</v>
       </c>
       <c r="B5" t="n">
-        <v>95011</v>
+        <v>100506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1038,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582159</v>
+        <v>582182</v>
       </c>
       <c r="R5" t="n">
-        <v>6542499</v>
+        <v>6542731</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,6 +1135,122 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122234131</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95011</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stavtorp, Stavtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>582159</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6542499</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sköldinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122234133</v>
+        <v>122234131</v>
       </c>
       <c r="B2" t="n">
-        <v>97188</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -715,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582206</v>
+        <v>582159</v>
       </c>
       <c r="R2" t="n">
-        <v>6542637</v>
+        <v>6542499</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122234130</v>
+        <v>122234132</v>
       </c>
       <c r="B3" t="n">
-        <v>91456</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,30 +797,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582050</v>
+        <v>582147</v>
       </c>
       <c r="R3" t="n">
-        <v>6542447</v>
+        <v>6542531</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122234132</v>
+        <v>122234130</v>
       </c>
       <c r="B4" t="n">
-        <v>95011</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,27 +908,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582147</v>
+        <v>582050</v>
       </c>
       <c r="R4" t="n">
-        <v>6542531</v>
+        <v>6542447</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,15 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234135</v>
+        <v>122234133</v>
       </c>
       <c r="B5" t="n">
-        <v>100506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,23 +1022,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -1066,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582182</v>
+        <v>582206</v>
       </c>
       <c r="R5" t="n">
-        <v>6542731</v>
+        <v>6542637</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,15 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234131</v>
+        <v>122234135</v>
       </c>
       <c r="B6" t="n">
-        <v>95011</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582159</v>
+        <v>582182</v>
       </c>
       <c r="R6" t="n">
-        <v>6542499</v>
+        <v>6542731</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1217,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 188-2025 artfynd.xlsx
+++ b/artfynd/A 188-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234131</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234132</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234130</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234133</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,8 +1251,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122234135</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>